--- a/diseases/d157/2000-2004.xlsx
+++ b/diseases/d157/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>31</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.6902898705305679</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>18</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4008134732112975</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.5344179642817301</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>8</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>19</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.4230808883897029</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>11</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>8</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.3340112276760813</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>16</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>17</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>26</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>25</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5538746076629216</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>21</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.4652546704368542</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>18</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>22</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.4874096547433711</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>15</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.332324764597753</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>15</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.332324764597753</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>14</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.3101697802912362</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>17</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>15</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.332324764597753</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>17</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>13</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>15</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.3305410692871375</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>17</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>13</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>13</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>8</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>8</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>13</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>13</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>24</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.5257774441038331</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>26</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.5695922311124859</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>18</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.3943330830778749</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>25</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.5476848376081596</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>14</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.3067035090605694</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>15</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.3286109025648957</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>10</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.2190739350432638</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>12</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>11</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>13</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>22</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>23</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.5038700505995067</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>33</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.7186814156063848</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>27</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.5880120673143148</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>21</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.4573427190222448</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>28</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>24</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.5226773931682798</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>22</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>16</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.3484515954455199</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>12</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.2613386965841399</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>9</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>17</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.3702298201608649</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>17</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.3702298201608649</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>25</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.5444556178836248</v>

--- a/diseases/d157/2000-2004.xlsx
+++ b/diseases/d157/2000-2004.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>863</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>863</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6902898705305679</v>
+        <v>2.793621337025877</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -813,42 +813,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -919,29 +919,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>863</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>863</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1047,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1144,22 +1144,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2000-02-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4008134732112975</v>
+        <v>0.6902898705305679</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1303,19 +1303,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2000-02-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1537,22 +1537,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2000-03-01</t>
+          <t>2000-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5344179642817301</v>
+        <v>0.4008134732112975</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1696,19 +1696,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2000-03-01</t>
+          <t>2000-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1930,22 +1930,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2000-04-01</t>
+          <t>2000-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4676157187465137</v>
+        <v>0.5344179642817301</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2000-04-01</t>
+          <t>2000-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2000-05-01</t>
+          <t>2000-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3562786428544867</v>
+        <v>0.4676157187465137</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2482,19 +2482,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2000-05-01</t>
+          <t>2000-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2716,22 +2716,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2000-06-01</t>
+          <t>2000-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1781393214272433</v>
+        <v>0.3562786428544867</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2875,19 +2875,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2000-06-01</t>
+          <t>2000-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2000-07-01</t>
+          <t>2000-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4230808883897029</v>
+        <v>0.1781393214272433</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3268,19 +3268,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2000-07-01</t>
+          <t>2000-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3502,22 +3502,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2449415669624596</v>
+        <v>0.4230808883897029</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3661,19 +3661,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3895,22 +3895,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2000-09-01</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1781393214272433</v>
+        <v>0.2449415669624596</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -4054,19 +4054,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2000-09-01</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4288,22 +4288,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2000-10-01</t>
+          <t>2000-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>0.08906966071362167</v>
+        <v>0.1781393214272433</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4447,19 +4447,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2000-10-01</t>
+          <t>2000-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4681,22 +4681,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2000-11-01</t>
+          <t>2000-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3340112276760813</v>
+        <v>0.08906966071362167</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4840,19 +4840,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2000-11-01</t>
+          <t>2000-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5074,22 +5074,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3562786428544867</v>
+        <v>0.3340112276760813</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5233,19 +5233,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5467,22 +5467,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2000-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3766347332107867</v>
+        <v>0.3562786428544867</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5626,19 +5626,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2000-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5860,22 +5860,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>26</v>
+        <v>830</v>
       </c>
       <c r="O28" t="n">
-        <v>26</v>
+        <v>830</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5760295919694386</v>
+        <v>2.659099275933675</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5922,42 +5922,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5989,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6019,38 +6019,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>26</v>
+        <v>830</v>
       </c>
       <c r="O29" t="n">
-        <v>26</v>
+        <v>830</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6110,17 +6110,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6156,42 +6156,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6253,22 +6253,22 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5538746076629216</v>
+        <v>0.3766347332107867</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6412,19 +6412,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6646,22 +6646,22 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4652546704368542</v>
+        <v>0.5760295919694386</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6805,19 +6805,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O33" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -7039,22 +7039,22 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O34" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3987897175173036</v>
+        <v>0.5538746076629216</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7198,19 +7198,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7432,22 +7432,22 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4874096547433711</v>
+        <v>0.4652546704368542</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7591,19 +7591,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -7825,22 +7825,22 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R38" t="n">
-        <v>0.332324764597753</v>
+        <v>0.3987897175173036</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1107749215325843</v>
+        <v>0.4874096547433711</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8377,19 +8377,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -9004,22 +9004,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3101697802912362</v>
+        <v>0.1107749215325843</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9163,19 +9163,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9397,22 +9397,22 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3766347332107867</v>
+        <v>0.332324764597753</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9556,19 +9556,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9790,22 +9790,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>0.332324764597753</v>
+        <v>0.3101697802912362</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9949,19 +9949,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -10183,22 +10183,22 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2203607128580917</v>
+        <v>0.3766347332107867</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10342,19 +10342,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O51" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -10576,22 +10576,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O52" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3746132118587558</v>
+        <v>0.332324764597753</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10735,19 +10735,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -10939,12 +10939,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10969,22 +10969,22 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>13</v>
+        <v>866</v>
       </c>
       <c r="O54" t="n">
-        <v>13</v>
+        <v>866</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2864689267155192</v>
+        <v>2.746104776422756</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11031,42 +11031,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11128,38 +11128,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>13</v>
+        <v>866</v>
       </c>
       <c r="O55" t="n">
-        <v>13</v>
+        <v>866</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11219,17 +11219,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11265,42 +11265,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11362,22 +11362,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>0.3305410692871375</v>
+        <v>0.2203607128580917</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11521,19 +11521,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11755,12 +11755,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -12541,22 +12541,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R62" t="n">
-        <v>0.2864689267155192</v>
+        <v>0.3305410692871375</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12700,19 +12700,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O63" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12934,22 +12934,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1762885702864733</v>
+        <v>0.3746132118587558</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13093,19 +13093,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13327,22 +13327,22 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1762885702864733</v>
+        <v>0.2864689267155192</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13486,19 +13486,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13720,22 +13720,22 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1762885702864733</v>
+        <v>0.2864689267155192</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13879,19 +13879,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14113,22 +14113,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O70" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R70" t="n">
-        <v>0.2864689267155192</v>
+        <v>0.1762885702864733</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14272,19 +14272,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14506,22 +14506,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R72" t="n">
-        <v>0.2864689267155192</v>
+        <v>0.1762885702864733</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14665,19 +14665,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14899,22 +14899,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="R74" t="n">
-        <v>0.5257774441038331</v>
+        <v>0.1762885702864733</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15058,19 +15058,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15292,22 +15292,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="R76" t="n">
-        <v>0.5695922311124859</v>
+        <v>0.2864689267155192</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15451,19 +15451,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O77" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15685,22 +15685,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O78" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3943330830778749</v>
+        <v>0.2864689267155192</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15844,19 +15844,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O79" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -16048,12 +16048,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>25</v>
+        <v>1039</v>
       </c>
       <c r="O80" t="n">
-        <v>25</v>
+        <v>1039</v>
       </c>
       <c r="R80" t="n">
-        <v>0.5476848376081596</v>
+        <v>3.263551544420015</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -16102,12 +16102,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -16140,42 +16140,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16207,12 +16207,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -16237,38 +16237,38 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>25</v>
+        <v>1039</v>
       </c>
       <c r="O81" t="n">
-        <v>25</v>
+        <v>1039</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -16374,42 +16374,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16471,22 +16471,22 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O82" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="R82" t="n">
-        <v>0.3067035090605694</v>
+        <v>0.5257774441038331</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16630,19 +16630,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O83" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16864,22 +16864,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O84" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="R84" t="n">
-        <v>0.3286109025648957</v>
+        <v>0.5695922311124859</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -17023,19 +17023,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O85" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17257,22 +17257,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O86" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2190739350432638</v>
+        <v>0.3943330830778749</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17416,19 +17416,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O87" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17650,22 +17650,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="R88" t="n">
-        <v>0.2628887220519165</v>
+        <v>0.5476848376081596</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17809,19 +17809,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O89" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18043,22 +18043,22 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R90" t="n">
-        <v>0.2409813285475902</v>
+        <v>0.3067035090605694</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18202,19 +18202,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O91" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18436,22 +18436,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O92" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R92" t="n">
-        <v>0.284796115556243</v>
+        <v>0.3286109025648957</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18595,19 +18595,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18829,22 +18829,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O94" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R94" t="n">
-        <v>0.4819626570951804</v>
+        <v>0.2190739350432638</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18988,19 +18988,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -19222,22 +19222,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O96" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>0.5038700505995067</v>
+        <v>0.2628887220519165</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19381,19 +19381,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O97" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19615,22 +19615,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O98" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="R98" t="n">
-        <v>0.7186814156063848</v>
+        <v>0.2409813285475902</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19774,19 +19774,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O99" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20008,22 +20008,22 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O100" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="R100" t="n">
-        <v>0.5880120673143148</v>
+        <v>0.284796115556243</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20167,19 +20167,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O101" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20401,22 +20401,22 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R102" t="n">
-        <v>0.4573427190222448</v>
+        <v>0.4819626570951804</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20560,19 +20560,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20794,22 +20794,22 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O104" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R104" t="n">
-        <v>0.6097902920296598</v>
+        <v>0.5038700505995067</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O105" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21187,22 +21187,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="O106" t="n">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="R106" t="n">
-        <v>0.5226773931682798</v>
+        <v>2.667066882303847</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21211,12 +21211,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21249,42 +21249,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21316,12 +21316,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21346,38 +21346,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="O107" t="n">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -21387,12 +21387,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21437,17 +21437,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D153_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21483,42 +21483,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21580,22 +21580,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O108" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="R108" t="n">
-        <v>0.4791209437375898</v>
+        <v>0.7186814156063848</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21739,19 +21739,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O109" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21973,22 +21973,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="O110" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3484515954455199</v>
+        <v>0.5880120673143148</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -22132,19 +22132,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="O111" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22366,22 +22366,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O112" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="R112" t="n">
-        <v>0.2613386965841399</v>
+        <v>0.4573427190222448</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22525,19 +22525,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O113" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22759,22 +22759,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O114" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="R114" t="n">
-        <v>0.1960040224381049</v>
+        <v>0.6097902920296598</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22918,19 +22918,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O115" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23152,22 +23152,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="O116" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3702298201608649</v>
+        <v>0.5226773931682798</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23311,19 +23311,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="O117" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23545,22 +23545,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O118" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R118" t="n">
-        <v>0.3702298201608649</v>
+        <v>0.4791209437375898</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23704,19 +23704,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O119" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23938,22 +23938,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O120" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="R120" t="n">
-        <v>0.5444556178836248</v>
+        <v>0.3484515954455199</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -24097,19 +24097,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O121" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24268,6 +24268,1971 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>12</v>
+      </c>
+      <c r="O122" t="n">
+        <v>12</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.2613386965841399</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>12</v>
+      </c>
+      <c r="O123" t="n">
+        <v>12</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>9</v>
+      </c>
+      <c r="O124" t="n">
+        <v>9</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.1960040224381049</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>9</v>
+      </c>
+      <c r="O125" t="n">
+        <v>9</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>17</v>
+      </c>
+      <c r="O126" t="n">
+        <v>17</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3702298201608649</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>17</v>
+      </c>
+      <c r="O127" t="n">
+        <v>17</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>17</v>
+      </c>
+      <c r="O128" t="n">
+        <v>17</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3702298201608649</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>17</v>
+      </c>
+      <c r="O129" t="n">
+        <v>17</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>25</v>
+      </c>
+      <c r="O130" t="n">
+        <v>25</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.5444556178836248</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>25</v>
+      </c>
+      <c r="O131" t="n">
+        <v>25</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -24389,7 +26354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -24399,7 +26364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24419,7 +26384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -24429,7 +26394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24451,7 +26416,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1013</v>
+        <v>5468</v>
       </c>
     </row>
     <row r="16">
